--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-oral-health</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-oral-health</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4084" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4084" uniqueCount="566">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3916,7 +3908,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3934,23 +3926,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3977,10 +3969,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3988,13 +3980,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -4038,7 +4030,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -4056,10 +4048,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -4101,10 +4093,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4112,14 +4104,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4141,16 +4133,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4160,29 +4152,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4199,7 +4191,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4214,30 +4206,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4260,19 +4252,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4321,7 +4313,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4336,19 +4328,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4356,10 +4348,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4382,16 +4374,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4441,7 +4433,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4462,13 +4454,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4476,14 +4468,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4502,19 +4494,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4563,7 +4555,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4578,19 +4570,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4598,14 +4590,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4624,19 +4616,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4685,7 +4677,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4700,19 +4692,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4720,10 +4712,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4746,16 +4738,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4805,7 +4797,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4826,13 +4818,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4840,10 +4832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4866,17 +4858,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4925,7 +4917,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4940,19 +4932,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4960,10 +4952,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4986,19 +4978,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -5035,17 +5027,17 @@
         <v>18</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5054,7 +5046,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5063,30 +5055,30 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>18</v>
@@ -5108,19 +5100,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -5169,7 +5161,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5178,7 +5170,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -5187,27 +5179,27 @@
         <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5230,13 +5222,13 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5287,7 +5279,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5311,7 +5303,7 @@
         <v>18</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>18</v>
@@ -5322,10 +5314,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5354,7 +5346,7 @@
         <v>137</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>139</v>
@@ -5395,19 +5387,19 @@
         <v>18</v>
       </c>
       <c r="AB27" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AC27" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AC27" t="s" s="2">
+      <c r="AD27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5431,7 +5423,7 @@
         <v>18</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5442,10 +5434,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5468,19 +5460,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -5529,7 +5521,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5550,10 +5542,10 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>18</v>
@@ -5564,10 +5556,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5593,20 +5585,20 @@
         <v>110</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="P29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="R29" t="s" s="2">
         <v>18</v>
@@ -5630,28 +5622,28 @@
         <v>179</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5672,10 +5664,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5686,10 +5678,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5712,17 +5704,17 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -5732,46 +5724,46 @@
         <v>18</v>
       </c>
       <c r="S30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5792,10 +5784,10 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
@@ -5806,10 +5798,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5835,14 +5827,14 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5852,46 +5844,46 @@
         <v>18</v>
       </c>
       <c r="S31" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5900,7 +5892,7 @@
         <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
@@ -5912,10 +5904,10 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>18</v>
@@ -5926,10 +5918,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5955,16 +5947,16 @@
         <v>110</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -6013,7 +6005,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6034,10 +6026,10 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -6048,10 +6040,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6077,16 +6069,16 @@
         <v>188</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -6111,14 +6103,14 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
       </c>
@@ -6135,7 +6127,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6144,7 +6136,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -6159,7 +6151,7 @@
         <v>133</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -6170,14 +6162,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6199,16 +6191,16 @@
         <v>188</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -6233,14 +6225,14 @@
         <v>18</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>18</v>
       </c>
@@ -6257,7 +6249,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6275,27 +6267,27 @@
         <v>18</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6318,19 +6310,19 @@
         <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
@@ -6379,7 +6371,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6400,10 +6392,10 @@
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>18</v>
@@ -6414,10 +6406,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6443,13 +6435,13 @@
         <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6475,14 +6467,14 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
       </c>
@@ -6499,7 +6491,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6517,27 +6509,27 @@
         <v>18</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>389</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6563,16 +6555,16 @@
         <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6597,14 +6589,14 @@
         <v>18</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>18</v>
       </c>
@@ -6621,7 +6613,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6642,10 +6634,10 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6656,10 +6648,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6682,16 +6674,16 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6741,7 +6733,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6759,27 +6751,27 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>407</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6802,16 +6794,16 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6861,7 +6853,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6879,27 +6871,27 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6922,19 +6914,19 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6983,7 +6975,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6995,19 +6987,19 @@
         <v>18</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -7018,10 +7010,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7044,13 +7036,13 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7101,7 +7093,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7125,7 +7117,7 @@
         <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7136,10 +7128,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7168,7 +7160,7 @@
         <v>137</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -7221,7 +7213,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7245,7 +7237,7 @@
         <v>18</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -7256,14 +7248,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7285,10 +7277,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>139</v>
@@ -7343,7 +7335,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7378,10 +7370,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7404,13 +7396,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7461,7 +7453,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7470,7 +7462,7 @@
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>102</v>
@@ -7482,10 +7474,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7496,10 +7488,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7522,13 +7514,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7579,7 +7571,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7588,7 +7580,7 @@
         <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>102</v>
@@ -7600,10 +7592,10 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7614,10 +7606,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7643,16 +7635,16 @@
         <v>188</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7680,11 +7672,11 @@
         <v>114</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7701,7 +7693,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7719,13 +7711,13 @@
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AN46" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7736,10 +7728,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7765,16 +7757,16 @@
         <v>188</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7799,14 +7791,14 @@
         <v>18</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>18</v>
       </c>
@@ -7823,7 +7815,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7841,13 +7833,13 @@
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="AN47" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>18</v>
@@ -7858,10 +7850,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7884,17 +7876,17 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7943,7 +7935,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7967,7 +7959,7 @@
         <v>18</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>18</v>
@@ -7978,10 +7970,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8004,13 +7996,13 @@
         <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8061,7 +8053,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8082,10 +8074,10 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>18</v>
@@ -8096,10 +8088,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8122,16 +8114,16 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8181,7 +8173,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8202,10 +8194,10 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8216,10 +8208,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8242,16 +8234,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8301,7 +8293,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8322,10 +8314,10 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>18</v>
@@ -8336,10 +8328,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8362,19 +8354,19 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8411,17 +8403,17 @@
         <v>18</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8442,10 +8434,10 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8456,10 +8448,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8482,13 +8474,13 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8539,7 +8531,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8563,7 +8555,7 @@
         <v>18</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8574,10 +8566,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8606,7 +8598,7 @@
         <v>137</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -8659,7 +8651,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8683,7 +8675,7 @@
         <v>18</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
@@ -8694,14 +8686,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8723,10 +8715,10 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8781,7 +8773,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8816,10 +8808,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8845,16 +8837,16 @@
         <v>188</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N56" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="O56" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8879,14 +8871,14 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y56" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y56" t="s" s="2">
+      <c r="Z56" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
       </c>
@@ -8903,7 +8895,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>90</v>
@@ -8921,16 +8913,16 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>18</v>
@@ -8938,10 +8930,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8964,19 +8956,19 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -9025,7 +9017,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9043,27 +9035,27 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9089,16 +9081,16 @@
         <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="O58" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9123,14 +9115,14 @@
         <v>18</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y58" t="s" s="2">
+      <c r="Z58" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>18</v>
       </c>
@@ -9147,7 +9139,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9156,7 +9148,7 @@
         <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>102</v>
@@ -9171,7 +9163,7 @@
         <v>133</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>18</v>
@@ -9182,14 +9174,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9211,16 +9203,16 @@
         <v>188</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9245,14 +9237,14 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>18</v>
       </c>
@@ -9269,7 +9261,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9287,27 +9279,27 @@
         <v>18</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9333,16 +9325,16 @@
         <v>80</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N60" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9391,7 +9383,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9412,10 +9404,10 @@
         <v>18</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>18</v>
@@ -9426,13 +9418,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>18</v>
@@ -9454,19 +9446,19 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>18</v>
@@ -9515,7 +9507,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9536,10 +9528,10 @@
         <v>18</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9550,10 +9542,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9576,13 +9568,13 @@
         <v>18</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9633,7 +9625,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9657,7 +9649,7 @@
         <v>18</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9668,10 +9660,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9700,7 +9692,7 @@
         <v>137</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>139</v>
@@ -9753,7 +9745,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9777,7 +9769,7 @@
         <v>18</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
@@ -9788,14 +9780,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9817,10 +9809,10 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>139</v>
@@ -9875,7 +9867,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9910,10 +9902,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9939,16 +9931,16 @@
         <v>188</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N65" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -9958,7 +9950,7 @@
         <v>18</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>18</v>
@@ -9973,14 +9965,14 @@
         <v>18</v>
       </c>
       <c r="X65" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y65" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y65" t="s" s="2">
+      <c r="Z65" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z65" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA65" t="s" s="2">
         <v>18</v>
       </c>
@@ -9997,7 +9989,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>90</v>
@@ -10015,16 +10007,16 @@
         <v>18</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>18</v>
@@ -10032,10 +10024,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10058,19 +10050,19 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="O66" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -10119,7 +10111,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10137,27 +10129,27 @@
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10183,16 +10175,16 @@
         <v>188</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N67" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10217,14 +10209,14 @@
         <v>18</v>
       </c>
       <c r="X67" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y67" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y67" t="s" s="2">
+      <c r="Z67" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>18</v>
       </c>
@@ -10241,7 +10233,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10250,7 +10242,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -10265,7 +10257,7 @@
         <v>133</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>18</v>
@@ -10276,14 +10268,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10305,16 +10297,16 @@
         <v>188</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -10339,14 +10331,14 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
       </c>
@@ -10363,7 +10355,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10381,27 +10373,27 @@
         <v>18</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10427,16 +10419,16 @@
         <v>80</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N69" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -10485,7 +10477,7 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10506,10 +10498,10 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10520,13 +10512,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C70" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>18</v>
@@ -10548,19 +10540,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -10609,7 +10601,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10630,10 +10622,10 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10644,10 +10636,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10670,13 +10662,13 @@
         <v>18</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10727,7 +10719,7 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10751,7 +10743,7 @@
         <v>18</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10762,10 +10754,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10794,7 +10786,7 @@
         <v>137</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>139</v>
@@ -10847,7 +10839,7 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10871,7 +10863,7 @@
         <v>18</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>18</v>
@@ -10882,14 +10874,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10911,10 +10903,10 @@
         <v>136</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>139</v>
@@ -10969,7 +10961,7 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11004,10 +10996,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11033,16 +11025,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N74" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="O74" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -11052,7 +11044,7 @@
         <v>18</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>18</v>
@@ -11067,14 +11059,14 @@
         <v>18</v>
       </c>
       <c r="X74" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y74" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y74" t="s" s="2">
+      <c r="Z74" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>18</v>
       </c>
@@ -11091,7 +11083,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>90</v>
@@ -11109,16 +11101,16 @@
         <v>18</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>18</v>
@@ -11126,10 +11118,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11152,19 +11144,19 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -11213,7 +11205,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11231,27 +11223,27 @@
         <v>18</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11277,16 +11269,16 @@
         <v>188</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="O76" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -11311,14 +11303,14 @@
         <v>18</v>
       </c>
       <c r="X76" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y76" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y76" t="s" s="2">
+      <c r="Z76" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>18</v>
       </c>
@@ -11335,7 +11327,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11344,7 +11336,7 @@
         <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>102</v>
@@ -11359,7 +11351,7 @@
         <v>133</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>18</v>
@@ -11370,14 +11362,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11399,16 +11391,16 @@
         <v>188</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
@@ -11433,14 +11425,14 @@
         <v>18</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>18</v>
       </c>
@@ -11457,7 +11449,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11475,27 +11467,27 @@
         <v>18</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11521,16 +11513,16 @@
         <v>80</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M78" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N78" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>18</v>
@@ -11579,7 +11571,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11600,10 +11592,10 @@
         <v>18</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>18</v>
@@ -11614,13 +11606,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>18</v>
@@ -11642,19 +11634,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>18</v>
@@ -11703,7 +11695,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11724,10 +11716,10 @@
         <v>18</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11738,10 +11730,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11764,13 +11756,13 @@
         <v>18</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11821,7 +11813,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11845,7 +11837,7 @@
         <v>18</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>18</v>
@@ -11856,10 +11848,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11888,7 +11880,7 @@
         <v>137</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>139</v>
@@ -11941,7 +11933,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11965,7 +11957,7 @@
         <v>18</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>18</v>
@@ -11976,14 +11968,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12005,10 +11997,10 @@
         <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>139</v>
@@ -12063,7 +12055,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12098,10 +12090,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12127,16 +12119,16 @@
         <v>188</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N83" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="O83" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>18</v>
@@ -12146,7 +12138,7 @@
         <v>18</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>18</v>
@@ -12161,14 +12153,14 @@
         <v>18</v>
       </c>
       <c r="X83" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y83" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y83" t="s" s="2">
+      <c r="Z83" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z83" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA83" t="s" s="2">
         <v>18</v>
       </c>
@@ -12185,7 +12177,7 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>90</v>
@@ -12203,16 +12195,16 @@
         <v>18</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>18</v>
@@ -12220,10 +12212,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12246,19 +12238,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12307,7 +12299,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12325,27 +12317,27 @@
         <v>18</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP84" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12371,16 +12363,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N85" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="O85" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>18</v>
@@ -12405,14 +12397,14 @@
         <v>18</v>
       </c>
       <c r="X85" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y85" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y85" t="s" s="2">
+      <c r="Z85" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>18</v>
       </c>
@@ -12429,7 +12421,7 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12438,7 +12430,7 @@
         <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>102</v>
@@ -12453,7 +12445,7 @@
         <v>133</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>18</v>
@@ -12464,14 +12456,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12493,16 +12485,16 @@
         <v>188</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -12527,14 +12519,14 @@
         <v>18</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>18</v>
       </c>
@@ -12551,7 +12543,7 @@
         <v>18</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12569,27 +12561,27 @@
         <v>18</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM86" t="s" s="2">
+      <c r="AN86" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12615,16 +12607,16 @@
         <v>80</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N87" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O87" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>18</v>
@@ -12673,7 +12665,7 @@
         <v>18</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12694,10 +12686,10 @@
         <v>18</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>18</v>
@@ -12708,13 +12700,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>18</v>
@@ -12736,19 +12728,19 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>18</v>
@@ -12797,7 +12789,7 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12818,10 +12810,10 @@
         <v>18</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>18</v>
@@ -12832,10 +12824,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12858,13 +12850,13 @@
         <v>18</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12915,7 +12907,7 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12939,7 +12931,7 @@
         <v>18</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>18</v>
@@ -12950,10 +12942,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12982,7 +12974,7 @@
         <v>137</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>139</v>
@@ -13035,7 +13027,7 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13059,7 +13051,7 @@
         <v>18</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>18</v>
@@ -13070,14 +13062,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13099,10 +13091,10 @@
         <v>136</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>139</v>
@@ -13157,7 +13149,7 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13192,10 +13184,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13221,16 +13213,16 @@
         <v>188</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N92" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>18</v>
@@ -13240,7 +13232,7 @@
         <v>18</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>18</v>
@@ -13255,14 +13247,14 @@
         <v>18</v>
       </c>
       <c r="X92" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y92" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y92" t="s" s="2">
+      <c r="Z92" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>18</v>
       </c>
@@ -13279,7 +13271,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>90</v>
@@ -13297,16 +13289,16 @@
         <v>18</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>18</v>
@@ -13314,10 +13306,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13340,19 +13332,19 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>18</v>
@@ -13401,7 +13393,7 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13419,27 +13411,27 @@
         <v>18</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13465,16 +13457,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="O94" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>18</v>
@@ -13499,14 +13491,14 @@
         <v>18</v>
       </c>
       <c r="X94" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y94" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y94" t="s" s="2">
+      <c r="Z94" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>18</v>
       </c>
@@ -13523,7 +13515,7 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13532,7 +13524,7 @@
         <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>102</v>
@@ -13547,7 +13539,7 @@
         <v>133</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>18</v>
@@ -13558,14 +13550,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13587,16 +13579,16 @@
         <v>188</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>18</v>
@@ -13621,14 +13613,14 @@
         <v>18</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>18</v>
       </c>
@@ -13645,7 +13637,7 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13663,27 +13655,27 @@
         <v>18</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13709,16 +13701,16 @@
         <v>80</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N96" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>18</v>
@@ -13767,7 +13759,7 @@
         <v>18</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13788,10 +13780,10 @@
         <v>18</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>18</v>
@@ -13802,13 +13794,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>18</v>
@@ -13830,19 +13822,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>18</v>
@@ -13891,7 +13883,7 @@
         <v>18</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13912,10 +13904,10 @@
         <v>18</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>18</v>
@@ -13926,10 +13918,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13952,13 +13944,13 @@
         <v>18</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14009,7 +14001,7 @@
         <v>18</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14033,7 +14025,7 @@
         <v>18</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>18</v>
@@ -14044,10 +14036,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14076,7 +14068,7 @@
         <v>137</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>139</v>
@@ -14129,7 +14121,7 @@
         <v>18</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14153,7 +14145,7 @@
         <v>18</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>18</v>
@@ -14164,14 +14156,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14193,10 +14185,10 @@
         <v>136</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>139</v>
@@ -14251,7 +14243,7 @@
         <v>18</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14286,10 +14278,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14315,16 +14307,16 @@
         <v>188</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N101" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="O101" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>18</v>
@@ -14334,7 +14326,7 @@
         <v>18</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>18</v>
@@ -14349,14 +14341,14 @@
         <v>18</v>
       </c>
       <c r="X101" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y101" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y101" t="s" s="2">
+      <c r="Z101" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>18</v>
       </c>
@@ -14373,7 +14365,7 @@
         <v>18</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>90</v>
@@ -14391,16 +14383,16 @@
         <v>18</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>18</v>
@@ -14408,10 +14400,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14434,19 +14426,19 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M102" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="O102" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>18</v>
@@ -14495,7 +14487,7 @@
         <v>18</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14513,27 +14505,27 @@
         <v>18</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN102" t="s" s="2">
+      <c r="AO102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14559,16 +14551,16 @@
         <v>188</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N103" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="O103" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>18</v>
@@ -14593,14 +14585,14 @@
         <v>18</v>
       </c>
       <c r="X103" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Y103" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Y103" t="s" s="2">
+      <c r="Z103" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Z103" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AA103" t="s" s="2">
         <v>18</v>
       </c>
@@ -14617,7 +14609,7 @@
         <v>18</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14626,7 +14618,7 @@
         <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
@@ -14641,7 +14633,7 @@
         <v>133</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>18</v>
@@ -14652,14 +14644,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14681,16 +14673,16 @@
         <v>188</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>18</v>
@@ -14715,14 +14707,14 @@
         <v>18</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z104" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA104" t="s" s="2">
         <v>18</v>
       </c>
@@ -14739,7 +14731,7 @@
         <v>18</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14757,27 +14749,27 @@
         <v>18</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM104" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM104" t="s" s="2">
+      <c r="AN104" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN104" t="s" s="2">
+      <c r="AO104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP104" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14803,16 +14795,16 @@
         <v>80</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M105" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N105" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O105" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>18</v>
@@ -14861,7 +14853,7 @@
         <v>18</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14882,10 +14874,10 @@
         <v>18</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-oral-health.xlsx
+++ b/StructureDefinition-onc-oral-health.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
